--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_18/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_18/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>50.71096070558761</v>
+        <v>52.89201311789211</v>
       </c>
       <c r="B2" t="n">
-        <v>166.9809240929542</v>
+        <v>114.2061005784972</v>
       </c>
       <c r="C2" t="n">
-        <v>49.30554835286635</v>
+        <v>45.4205450746652</v>
       </c>
       <c r="D2" t="n">
-        <v>11.21483456612283</v>
+        <v>11.48075322454395</v>
       </c>
       <c r="E2" t="n">
-        <v>4.562006623444558</v>
+        <v>4.955868441350977</v>
       </c>
       <c r="F2" t="n">
-        <v>6.439473971248886</v>
+        <v>6.770859590773329</v>
       </c>
       <c r="G2" t="n">
-        <v>0.399148028140201</v>
+        <v>0.3333454842982386</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0001224329744813115</v>
+        <v>-0.00183061124163492</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5765029615241554</v>
+        <v>-0.5792389477886857</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.1414352679061492</v>
+        <v>-0.1473015012360963</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0001824506351333963</v>
+        <v>-0.0003028635709031783</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2538144125430051</v>
+        <v>-0.2716900983841908</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1071685304455079</v>
+        <v>-0.0008461981087704018</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99.99999998640547</v>
+        <v>99.99999951495073</v>
       </c>
       <c r="B3" t="n">
-        <v>148.087910778931</v>
+        <v>104.7990224928112</v>
       </c>
       <c r="C3" t="n">
-        <v>49.78962256289727</v>
+        <v>45.42163244926434</v>
       </c>
       <c r="D3" t="n">
-        <v>6.03542668192557</v>
+        <v>7.232835126674212</v>
       </c>
       <c r="E3" t="n">
-        <v>3.532804838222261</v>
+        <v>4.936553113084134</v>
       </c>
       <c r="F3" t="n">
-        <v>15.56278903754595</v>
+        <v>15.91121356893521</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03487546042679585</v>
+        <v>0.03439393311981314</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8597904792965944</v>
+        <v>-0.8404179153397967</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9103306046936718</v>
+        <v>-0.9000561497444033</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9364923847257349</v>
+        <v>-0.9247321607991908</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0002354795490608075</v>
+        <v>-0.06430080330670514</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6220069728924841</v>
+        <v>-0.5874999965440239</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.09548420693195332</v>
+        <v>-0.001083443475857065</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99.99999998640547</v>
+        <v>63.19830081788315</v>
       </c>
       <c r="B4" t="n">
-        <v>142.7567015695406</v>
+        <v>113.7298300854208</v>
       </c>
       <c r="C4" t="n">
-        <v>49.78962256289727</v>
+        <v>45.43496601373077</v>
       </c>
       <c r="D4" t="n">
-        <v>6.03542668192557</v>
+        <v>10.8662419245108</v>
       </c>
       <c r="E4" t="n">
-        <v>4.563215775019894</v>
+        <v>4.493339379681635</v>
       </c>
       <c r="F4" t="n">
-        <v>15.56278903754595</v>
+        <v>8.312439734793115</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03487546042679585</v>
+        <v>0.1714105253624812</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8597904792965944</v>
+        <v>-0.4012184792715422</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9103306046936718</v>
+        <v>-0.7131542198964256</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9364923847257349</v>
+        <v>-0.5661553783882894</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0002354795490608075</v>
+        <v>-0.003748565376543461</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6220069728924841</v>
+        <v>-0.3252878933274175</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.09548420693195332</v>
+        <v>-0.00399258481398726</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>50.71096070558761</v>
+        <v>65.21467179247611</v>
       </c>
       <c r="B5" t="n">
-        <v>152.0643338555684</v>
+        <v>104.2076295417671</v>
       </c>
       <c r="C5" t="n">
-        <v>49.30554835286635</v>
+        <v>45.41887449151285</v>
       </c>
       <c r="D5" t="n">
-        <v>11.21483456612283</v>
+        <v>10.78810366834889</v>
       </c>
       <c r="E5" t="n">
-        <v>4.562006623444558</v>
+        <v>4.140549808998201</v>
       </c>
       <c r="F5" t="n">
-        <v>6.439473971248886</v>
+        <v>8.658382288085104</v>
       </c>
       <c r="G5" t="n">
-        <v>0.399148028140201</v>
+        <v>0.1527935714933787</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0001224329744813115</v>
+        <v>-0.453792595751934</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5765029615241554</v>
+        <v>-0.7327679994093328</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1414352679061492</v>
+        <v>-0.6159785338440998</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0001824506351333963</v>
+        <v>-0.02131066741276683</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2538144125430051</v>
+        <v>-0.3396545365213922</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1071685304455079</v>
+        <v>-0.0004817072391657962</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67.08610668704024</v>
+        <v>85.77449110153873</v>
       </c>
       <c r="B6" t="n">
-        <v>145.1729027613802</v>
+        <v>114.0208132078782</v>
       </c>
       <c r="C6" t="n">
-        <v>49.64022834734979</v>
+        <v>45.42167519777728</v>
       </c>
       <c r="D6" t="n">
-        <v>9.8067968519007</v>
+        <v>8.709835177033121</v>
       </c>
       <c r="E6" t="n">
-        <v>3.387986209325125</v>
+        <v>4.480058712181439</v>
       </c>
       <c r="F6" t="n">
-        <v>8.80785363301989</v>
+        <v>12.53740862771902</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1400357964083573</v>
+        <v>0.05752700284876387</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5605812943452931</v>
+        <v>-0.7533249687431459</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7745060697138008</v>
+        <v>-0.8573080452204617</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7119716386767287</v>
+        <v>-0.8661396546085021</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.00741522277633063</v>
+        <v>-0.005256692779470186</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.376137894862409</v>
+        <v>-0.4861432490984634</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1028152146145221</v>
+        <v>-0.001092770424134248</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>57.56142647665506</v>
+        <v>83.59818200791611</v>
       </c>
       <c r="B7" t="n">
-        <v>143.9594019456768</v>
+        <v>86.22718941600019</v>
       </c>
       <c r="C7" t="n">
-        <v>48.7938901930133</v>
+        <v>45.45455003700378</v>
       </c>
       <c r="D7" t="n">
-        <v>10.89576875322185</v>
+        <v>8.91671537923874</v>
       </c>
       <c r="E7" t="n">
-        <v>2.891886508272901</v>
+        <v>4.505790934795317</v>
       </c>
       <c r="F7" t="n">
-        <v>7.387308844096085</v>
+        <v>12.06862824715559</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2473850609585632</v>
+        <v>0.06285563875509331</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3116875009652985</v>
+        <v>-0.7344560413586154</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6809527763339498</v>
+        <v>-0.8485860616104723</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4772968843769466</v>
+        <v>-0.8524213780237625</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.03529800656547726</v>
+        <v>-0.0005222822793558002</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3049878695354485</v>
+        <v>-0.4706370468064023</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07771643153199292</v>
+        <v>-0.008265462619007208</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>53.42629460595492</v>
+        <v>70.61143124431204</v>
       </c>
       <c r="B8" t="n">
-        <v>146.3739227000343</v>
+        <v>89.91147110667067</v>
       </c>
       <c r="C8" t="n">
-        <v>49.44034648676463</v>
+        <v>45.42822836601159</v>
       </c>
       <c r="D8" t="n">
-        <v>11.21172963612882</v>
+        <v>9.919457977690612</v>
       </c>
       <c r="E8" t="n">
-        <v>4.735723522404118</v>
+        <v>4.942853843129088</v>
       </c>
       <c r="F8" t="n">
-        <v>6.843246314123652</v>
+        <v>9.482121366892802</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3280092520931603</v>
+        <v>0.1140550921088487</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1424679758454161</v>
+        <v>-0.572004946945023</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6228103404983666</v>
+        <v>-0.7801335791252398</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2999204151435905</v>
+        <v>-0.7229341531497323</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.04126034709482214</v>
+        <v>-0.01591121215732962</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2740981461188198</v>
+        <v>-0.4045857343323402</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1071366306573498</v>
+        <v>-0.002522552584345722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>65.22647110614351</v>
+        <v>57.62833142598747</v>
       </c>
       <c r="B9" t="n">
-        <v>141.8917601308196</v>
+        <v>108.0938050423176</v>
       </c>
       <c r="C9" t="n">
-        <v>49.9189452151966</v>
+        <v>45.41942022755737</v>
       </c>
       <c r="D9" t="n">
-        <v>9.955273997501024</v>
+        <v>11.24821225452339</v>
       </c>
       <c r="E9" t="n">
-        <v>2.308502298240974</v>
+        <v>4.932931230530873</v>
       </c>
       <c r="F9" t="n">
-        <v>8.499713458399594</v>
+        <v>7.453779202138396</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1552224896963336</v>
+        <v>0.2414932976679307</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5230342510972612</v>
+        <v>-0.2245791903379962</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7596213095093328</v>
+        <v>-0.6523599775377533</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.678866776948869</v>
+        <v>-0.3903255019975719</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.008643545385041695</v>
+        <v>-0.009898495676124434</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3622462874008321</v>
+        <v>-0.2964071735525333</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.08973095473205253</v>
+        <v>-0.0006007769216077874</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>68.58189506000932</v>
+        <v>69.4316842615428</v>
       </c>
       <c r="B10" t="n">
-        <v>156.2361870047625</v>
+        <v>89.96085157005217</v>
       </c>
       <c r="C10" t="n">
-        <v>48.86241379049445</v>
+        <v>45.4552849045422</v>
       </c>
       <c r="D10" t="n">
-        <v>9.844751837286198</v>
+        <v>9.963474951182372</v>
       </c>
       <c r="E10" t="n">
-        <v>3.907040636894439</v>
+        <v>4.708097646166151</v>
       </c>
       <c r="F10" t="n">
-        <v>9.077579565989652</v>
+        <v>9.260807164477944</v>
       </c>
       <c r="G10" t="n">
-        <v>0.129289645985133</v>
+        <v>0.1211719801063209</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5878556414406951</v>
+        <v>-0.5505490189287257</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.785521887973334</v>
+        <v>-0.7715777385761036</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7354347281605641</v>
+        <v>-0.7043763864529865</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0275761994838599</v>
+        <v>-0.001824107769055975</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3873115383097219</v>
+        <v>-0.3957376319615711</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.08239608653142277</v>
+        <v>-0.008425797354661008</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95.61439890317709</v>
+        <v>97.65256592298405</v>
       </c>
       <c r="B11" t="n">
-        <v>151.1166714625664</v>
+        <v>114.2043134333062</v>
       </c>
       <c r="C11" t="n">
-        <v>47.9768950249783</v>
+        <v>45.42167753863553</v>
       </c>
       <c r="D11" t="n">
-        <v>6.881215463035083</v>
+        <v>7.696712073245538</v>
       </c>
       <c r="E11" t="n">
-        <v>3.505652785333848</v>
+        <v>4.109318213145529</v>
       </c>
       <c r="F11" t="n">
-        <v>14.5695170444106</v>
+        <v>15.36906270216115</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04048301309783291</v>
+        <v>0.03721115404834333</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.840976858026503</v>
+        <v>-0.8293411554060827</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9004041487849329</v>
+        <v>-0.8943364657148466</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9250021931323208</v>
+        <v>-0.9177520360381893</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.03070823938105912</v>
+        <v>-0.09981993719901809</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5892462269930661</v>
+        <v>-0.5707745322012613</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.07712257800772331</v>
+        <v>-0.001093281156842874</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>62.06744056993519</v>
+        <v>72.215045173802</v>
       </c>
       <c r="B12" t="n">
-        <v>158.7013353070467</v>
+        <v>89.96085157005217</v>
       </c>
       <c r="C12" t="n">
-        <v>48.8462339318864</v>
+        <v>45.4552849045422</v>
       </c>
       <c r="D12" t="n">
-        <v>10.89614425567167</v>
+        <v>9.959461273642944</v>
       </c>
       <c r="E12" t="n">
-        <v>2.94794911904671</v>
+        <v>4.700502940001774</v>
       </c>
       <c r="F12" t="n">
-        <v>8.146810655149748</v>
+        <v>9.817185392249831</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1873188048369274</v>
+        <v>0.1053329524284606</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4478741472381744</v>
+        <v>-0.5989401561702902</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7306043317391647</v>
+        <v>-0.7910303698658629</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6099130616755796</v>
+        <v>-0.7457935367605513</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1055524371938967</v>
+        <v>-0.02036701877644989</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3386481090163452</v>
+        <v>-0.4030725178334271</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.08129112183300478</v>
+        <v>-0.008425797354661008</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>60.95115727335774</v>
+        <v>53.8790684859166</v>
       </c>
       <c r="B13" t="n">
-        <v>144.0152345657771</v>
+        <v>112.9488317880823</v>
       </c>
       <c r="C13" t="n">
-        <v>48.7957901891394</v>
+        <v>45.91115259541964</v>
       </c>
       <c r="D13" t="n">
-        <v>10.5566851824074</v>
+        <v>11.35555605110292</v>
       </c>
       <c r="E13" t="n">
-        <v>4.544407092566564</v>
+        <v>3.841413075659375</v>
       </c>
       <c r="F13" t="n">
-        <v>7.865975104316931</v>
+        <v>6.919226561617386</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1996431635138365</v>
+        <v>0.310993669841846</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4182346615185575</v>
+        <v>-0.05474065814178467</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.71961871264638</v>
+        <v>-0.5961346061102074</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5819540747458158</v>
+        <v>-0.2068245723184295</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.02803706802929596</v>
+        <v>-0.003894097343268943</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.330309394952544</v>
+        <v>-0.2790930136443744</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0778461872175852</v>
+        <v>-0.1078878390006502</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>82.71913452835764</v>
+        <v>95.12027956544395</v>
       </c>
       <c r="B14" t="n">
-        <v>167.792880905135</v>
+        <v>114.2043134333062</v>
       </c>
       <c r="C14" t="n">
-        <v>48.80260767211551</v>
+        <v>45.42167753863553</v>
       </c>
       <c r="D14" t="n">
-        <v>9.175402343998195</v>
+        <v>7.635598762077638</v>
       </c>
       <c r="E14" t="n">
-        <v>4.604370522366101</v>
+        <v>4.109318213145529</v>
       </c>
       <c r="F14" t="n">
-        <v>11.90806082835928</v>
+        <v>14.66395865634795</v>
       </c>
       <c r="G14" t="n">
-        <v>0.06658307895063018</v>
+        <v>0.0405377038665126</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7598533075121434</v>
+        <v>-0.8162719542392075</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8603537968595343</v>
+        <v>-0.8877451803865803</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8706306657331991</v>
+        <v>-0.909337102261545</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1850701164671526</v>
+        <v>-0.00458287298791452</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.492917702927149</v>
+        <v>-0.5527319919037881</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.07831177089190208</v>
+        <v>-0.001093281156842874</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>87.54216444078659</v>
+        <v>54.49688538252734</v>
       </c>
       <c r="B15" t="n">
-        <v>161.4725036364361</v>
+        <v>110.3566080682459</v>
       </c>
       <c r="C15" t="n">
-        <v>49.30507089436064</v>
+        <v>46.07450785562202</v>
       </c>
       <c r="D15" t="n">
-        <v>8.031035727933368</v>
+        <v>11.29528553061932</v>
       </c>
       <c r="E15" t="n">
-        <v>4.55028241240828</v>
+        <v>4.24576145102988</v>
       </c>
       <c r="F15" t="n">
-        <v>12.78171793105978</v>
+        <v>7.008905575383262</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05457147762985773</v>
+        <v>0.2979394016111529</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7958848282654443</v>
+        <v>-0.08596173542090584</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8776829473165615</v>
+        <v>-0.6062352104882183</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8956848320734596</v>
+        <v>-0.2414421675584623</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.08212087233766917</v>
+        <v>-0.006188588276164812</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5289460726825814</v>
+        <v>-0.283726640368955</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1071564035577389</v>
+        <v>-0.1435289866811687</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>78.64705852506093</v>
+        <v>53.38710821001533</v>
       </c>
       <c r="B16" t="n">
-        <v>172.3339323435093</v>
+        <v>113.6142874572579</v>
       </c>
       <c r="C16" t="n">
-        <v>48.32257343588167</v>
+        <v>45.42178187948655</v>
       </c>
       <c r="D16" t="n">
-        <v>8.953383806685217</v>
+        <v>11.54285793506172</v>
       </c>
       <c r="E16" t="n">
-        <v>3.336973257017795</v>
+        <v>4.386067745884455</v>
       </c>
       <c r="F16" t="n">
-        <v>10.95364145730561</v>
+        <v>6.860556492172128</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07921932298840097</v>
+        <v>0.3220707210391102</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7226462307414347</v>
+        <v>-0.02877917963342292</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8432649454677001</v>
+        <v>-0.5877985558935347</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8434790157398085</v>
+        <v>-0.1777352478902292</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.04246039348171256</v>
+        <v>-0.01834125599398786</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.4624990112369057</v>
+        <v>-0.275403311575115</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.06676411613691018</v>
+        <v>-0.001116046433428802</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>69.7832397931987</v>
+        <v>57.03564163249958</v>
       </c>
       <c r="B17" t="n">
-        <v>141.6826914708712</v>
+        <v>107.7475248215677</v>
       </c>
       <c r="C17" t="n">
-        <v>49.05064370126518</v>
+        <v>45.51805257710803</v>
       </c>
       <c r="D17" t="n">
-        <v>10.09103672669915</v>
+        <v>11.10607636187469</v>
       </c>
       <c r="E17" t="n">
-        <v>4.503995191774874</v>
+        <v>4.884365736911864</v>
       </c>
       <c r="F17" t="n">
-        <v>9.374951968215443</v>
+        <v>7.328757098473203</v>
       </c>
       <c r="G17" t="n">
-        <v>0.12171273316626</v>
+        <v>0.2506844062361429</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6078900714582159</v>
+        <v>-0.2007942036452134</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.793684161568133</v>
+        <v>-0.6443154224672145</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7523158788464903</v>
+        <v>-0.365392246842009</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.09925321173682898</v>
+        <v>-0.0001373241030417173</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3962856672363433</v>
+        <v>-0.3027673122437469</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.09338500578651414</v>
+        <v>-0.02212056227811551</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>59.02733905539669</v>
+        <v>91.65039852423718</v>
       </c>
       <c r="B18" t="n">
-        <v>173.9379610593086</v>
+        <v>105.5899097620096</v>
       </c>
       <c r="C18" t="n">
-        <v>48.78662734019051</v>
+        <v>45.42167519777728</v>
       </c>
       <c r="D18" t="n">
-        <v>10.58238475057583</v>
+        <v>8.71383260137398</v>
       </c>
       <c r="E18" t="n">
-        <v>3.885425935634882</v>
+        <v>4.480534379355359</v>
       </c>
       <c r="F18" t="n">
-        <v>7.548018209454121</v>
+        <v>14.01223431609464</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2247493414270831</v>
+        <v>0.04604757791891639</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3609957178651267</v>
+        <v>-0.7956563531993636</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6986679507865949</v>
+        <v>-0.8774654751437193</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5264943752567205</v>
+        <v>-0.8956318405586162</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.001221634407790171</v>
+        <v>-0.1502610179835917</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3159383387166453</v>
+        <v>-0.5280090894851899</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.07722043239050574</v>
+        <v>-0.001092770424134248</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>75.55548068052217</v>
+        <v>78.04622224781465</v>
       </c>
       <c r="B19" t="n">
-        <v>153.9880648948571</v>
+        <v>124.9287638011028</v>
       </c>
       <c r="C19" t="n">
-        <v>49.3163873911985</v>
+        <v>45.41733660189379</v>
       </c>
       <c r="D19" t="n">
-        <v>9.6358742442929</v>
+        <v>9.779785150216796</v>
       </c>
       <c r="E19" t="n">
-        <v>4.043327776036939</v>
+        <v>4.976386330206545</v>
       </c>
       <c r="F19" t="n">
-        <v>10.44380190146642</v>
+        <v>11.00977692081762</v>
       </c>
       <c r="G19" t="n">
-        <v>0.09151329163517695</v>
+        <v>0.08006542300896234</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6884907184484815</v>
+        <v>-0.6761313920803789</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.82799118940071</v>
+        <v>-0.8225257760702287</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8174275771199835</v>
+        <v>-0.8080053030440123</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1296574304522499</v>
+        <v>-0.0599321644469074</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4394047091626623</v>
+        <v>-0.4310793335156794</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1073932712004967</v>
+        <v>-0.0001461676859181027</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>64.19817922008539</v>
+        <v>65.90855111363496</v>
       </c>
       <c r="B20" t="n">
-        <v>146.1863056399847</v>
+        <v>96.57434255987907</v>
       </c>
       <c r="C20" t="n">
-        <v>48.75680112660675</v>
+        <v>45.4351743559339</v>
       </c>
       <c r="D20" t="n">
-        <v>10.1259856579911</v>
+        <v>10.8662419245108</v>
       </c>
       <c r="E20" t="n">
-        <v>4.079402588082152</v>
+        <v>4.030583302098487</v>
       </c>
       <c r="F20" t="n">
-        <v>8.333673592758277</v>
+        <v>8.807128231194227</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1645590516005031</v>
+        <v>0.1471321935858017</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5003773833568681</v>
+        <v>-0.476610872412779</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.750793354114178</v>
+        <v>-0.7428159549920584</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6584668044652016</v>
+        <v>-0.6381582921359485</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0007575905759151518</v>
+        <v>-0.07403641095318803</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3545648753092462</v>
+        <v>-0.3569562800184556</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.07546127963758174</v>
+        <v>-0.004038041294667782</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>63.29913802210358</v>
+        <v>96.88764760908288</v>
       </c>
       <c r="B21" t="n">
-        <v>149.5706833647135</v>
+        <v>108.2045547286908</v>
       </c>
       <c r="C21" t="n">
-        <v>49.87330692855745</v>
+        <v>46.67759076368709</v>
       </c>
       <c r="D21" t="n">
-        <v>10.10245077215781</v>
+        <v>7.312894107016378</v>
       </c>
       <c r="E21" t="n">
-        <v>4.052686015676215</v>
+        <v>4.935217615745249</v>
       </c>
       <c r="F21" t="n">
-        <v>8.187134044099409</v>
+        <v>15.11414504043112</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1733241009725354</v>
+        <v>0.03814993104745341</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4793607287318585</v>
+        <v>-0.8255697536465658</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.742704449994152</v>
+        <v>-0.8924352833710786</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6392692414663178</v>
+        <v>-0.9153479933889668</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.00268893561557694</v>
+        <v>-0.003758216769227626</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3478489748702329</v>
+        <v>-0.5653244892147155</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.09217002601643329</v>
+        <v>-0.2751107120771824</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>97.26017475831731</v>
+        <v>89.05989405037263</v>
       </c>
       <c r="B22" t="n">
-        <v>148.0143992263827</v>
+        <v>125.3782568185237</v>
       </c>
       <c r="C22" t="n">
-        <v>48.83775146372753</v>
+        <v>45.41947112967691</v>
       </c>
       <c r="D22" t="n">
-        <v>6.846144269419273</v>
+        <v>8.330486798887939</v>
       </c>
       <c r="E22" t="n">
-        <v>4.598731453445509</v>
+        <v>4.091420288619482</v>
       </c>
       <c r="F22" t="n">
-        <v>14.99663014381634</v>
+        <v>13.25630488362712</v>
       </c>
       <c r="G22" t="n">
-        <v>0.03827549830001865</v>
+        <v>0.05058521642564202</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8483914631289267</v>
+        <v>-0.77846878178794</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9042661177747108</v>
+        <v>-0.8692043773201681</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9295829395977395</v>
+        <v>-0.8838897543912729</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1016424745482521</v>
+        <v>-0.0008771804915405834</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6015402873908154</v>
+        <v>-0.5095517451089049</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.08071183198270135</v>
+        <v>-0.0006118828385985597</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>56.67487500764474</v>
+        <v>59.31379550161095</v>
       </c>
       <c r="B23" t="n">
-        <v>146.3739227000343</v>
+        <v>104.0565336979675</v>
       </c>
       <c r="C23" t="n">
-        <v>49.44034648676463</v>
+        <v>45.42956382170537</v>
       </c>
       <c r="D23" t="n">
-        <v>11.07613716259617</v>
+        <v>10.94315989539756</v>
       </c>
       <c r="E23" t="n">
-        <v>3.996772246392499</v>
+        <v>4.174274031575628</v>
       </c>
       <c r="F23" t="n">
-        <v>7.310865891813133</v>
+        <v>7.658206031098118</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2626963235840697</v>
+        <v>0.2164964639923148</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2792291624959031</v>
+        <v>-0.287697136918959</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6694634127194475</v>
+        <v>-0.6741555572691826</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4442398644790113</v>
+        <v>-0.4553641061104644</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.06543389848805235</v>
+        <v>-0.005655196901279193</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2983652682427606</v>
+        <v>-0.3198534662620822</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1071366306573498</v>
+        <v>-0.002813924735717011</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>54.69022777497551</v>
+        <v>75.66262144876698</v>
       </c>
       <c r="B24" t="n">
-        <v>148.3288355940763</v>
+        <v>89.35187006862901</v>
       </c>
       <c r="C24" t="n">
-        <v>48.80237505009541</v>
+        <v>45.4552663641478</v>
       </c>
       <c r="D24" t="n">
-        <v>11.07882651039917</v>
+        <v>9.919306819204248</v>
       </c>
       <c r="E24" t="n">
-        <v>2.601002470839886</v>
+        <v>4.712125344154923</v>
       </c>
       <c r="F24" t="n">
-        <v>6.981493992104057</v>
+        <v>10.5280685331267</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2998839022011778</v>
+        <v>0.08932167639445106</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1998238482646565</v>
+        <v>-0.6457488695562844</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.6421495118683583</v>
+        <v>-0.8094743922869004</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.361506733461349</v>
+        <v>-0.783783254222479</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.02429153185027791</v>
+        <v>-0.04174476216603625</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.2835398150253882</v>
+        <v>-0.4140961778224648</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.07829588452808878</v>
+        <v>-0.008421752177703162</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>91.76790168041842</v>
+        <v>67.84370400820535</v>
       </c>
       <c r="B25" t="n">
-        <v>153.1850499760033</v>
+        <v>107.7842675961395</v>
       </c>
       <c r="C25" t="n">
-        <v>49.06041373469229</v>
+        <v>45.43013025823314</v>
       </c>
       <c r="D25" t="n">
-        <v>7.635880925282048</v>
+        <v>10.49283959952094</v>
       </c>
       <c r="E25" t="n">
-        <v>3.924849202545774</v>
+        <v>4.816975278033042</v>
       </c>
       <c r="F25" t="n">
-        <v>13.74126021343693</v>
+        <v>9.081141982933836</v>
       </c>
       <c r="G25" t="n">
-        <v>0.04650929049363653</v>
+        <v>0.1321628123160334</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.821405486096655</v>
+        <v>-0.5134930317301922</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8903604863474573</v>
+        <v>-0.7557198818859204</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9125673713220402</v>
+        <v>-0.6706831126664896</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1107420797148409</v>
+        <v>-0.01043182186170944</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5605126245230367</v>
+        <v>-0.3583863910584631</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.09405909819299252</v>
+        <v>-0.002937510887230654</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>80.56200775636529</v>
+        <v>62.03122048253525</v>
       </c>
       <c r="B26" t="n">
-        <v>167.792880905135</v>
+        <v>113.9817946461167</v>
       </c>
       <c r="C26" t="n">
-        <v>48.71885159046473</v>
+        <v>45.42076009108757</v>
       </c>
       <c r="D26" t="n">
-        <v>9.175402343998195</v>
+        <v>11.0284929982859</v>
       </c>
       <c r="E26" t="n">
-        <v>4.526624856546039</v>
+        <v>4.169842357223974</v>
       </c>
       <c r="F26" t="n">
-        <v>11.42328379889001</v>
+        <v>8.144783014971395</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0729533687698479</v>
+        <v>0.1837379559593017</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.7410241185728705</v>
+        <v>-0.3674604829141161</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8516131802641305</v>
+        <v>-0.7007829327406082</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.8570435786201521</v>
+        <v>-0.5333581381968387</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.1369850716099607</v>
+        <v>-0.01454293965954992</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.4768038155240449</v>
+        <v>-0.3169724459380636</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.07368889723451279</v>
+        <v>-0.0008931107827421514</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>97.92762939952992</v>
+        <v>60.1673241495834</v>
       </c>
       <c r="B27" t="n">
-        <v>148.5860456359378</v>
+        <v>104.0565336979675</v>
       </c>
       <c r="C27" t="n">
-        <v>46.47744683258746</v>
+        <v>45.41955034000563</v>
       </c>
       <c r="D27" t="n">
-        <v>6.96230890196443</v>
+        <v>10.94785267261233</v>
       </c>
       <c r="E27" t="n">
-        <v>3.877277085849932</v>
+        <v>4.174274031575628</v>
       </c>
       <c r="F27" t="n">
-        <v>15.217245777508</v>
+        <v>7.802936898522531</v>
       </c>
       <c r="G27" t="n">
-        <v>0.03745658548033785</v>
+        <v>0.2053916857217898</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8512281663158655</v>
+        <v>-0.3168959052810423</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.9057427481377015</v>
+        <v>-0.6843976242703269</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.9313133697721443</v>
+        <v>-0.4847972427167662</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.113598346282357</v>
+        <v>-0.02029325735502258</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.6065262201022462</v>
+        <v>-0.3262549311218755</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.07497987143259284</v>
+        <v>-0.0006291650921372294</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>56.35466826592747</v>
+        <v>58.48342448517355</v>
       </c>
       <c r="B28" t="n">
-        <v>145.9112528951647</v>
+        <v>113.6100214422858</v>
       </c>
       <c r="C28" t="n">
-        <v>49.08706472677525</v>
+        <v>45.45022980120469</v>
       </c>
       <c r="D28" t="n">
-        <v>10.7741868117267</v>
+        <v>11.27792896650137</v>
       </c>
       <c r="E28" t="n">
-        <v>3.879595236460883</v>
+        <v>4.48396213176559</v>
       </c>
       <c r="F28" t="n">
-        <v>7.17194191732878</v>
+        <v>7.603306775584485</v>
       </c>
       <c r="G28" t="n">
-        <v>0.2674584239165302</v>
+        <v>0.2287377878912948</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2676954994615194</v>
+        <v>-0.247860915286556</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6655448316550762</v>
+        <v>-0.6584072028781706</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4325001315299081</v>
+        <v>-0.4126413492801201</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.0004447452050172591</v>
+        <v>-0.006039622761205994</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.2959733015541354</v>
+        <v>-0.2916943994568616</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.09589790780631338</v>
+        <v>-0.007322865717387522</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>86.03246236878172</v>
+        <v>79.71905042848981</v>
       </c>
       <c r="B29" t="n">
-        <v>148.0188812178639</v>
+        <v>110.378647486988</v>
       </c>
       <c r="C29" t="n">
-        <v>48.83938972681601</v>
+        <v>41.56136578645207</v>
       </c>
       <c r="D29" t="n">
-        <v>8.031035727933368</v>
+        <v>9.77152670951995</v>
       </c>
       <c r="E29" t="n">
-        <v>4.598731453445509</v>
+        <v>4.976386330206545</v>
       </c>
       <c r="F29" t="n">
-        <v>12.40665511502589</v>
+        <v>11.36013941066714</v>
       </c>
       <c r="G29" t="n">
-        <v>0.05786876885825938</v>
+        <v>0.07433681307160443</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7855823511927158</v>
+        <v>-0.6953427676080791</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.872694410811194</v>
+        <v>-0.8309413054204561</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.888671859358405</v>
+        <v>-0.8229431326548058</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.03093196128244185</v>
+        <v>-0.007144245847015628</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.5176684929332696</v>
+        <v>-0.4429982343029899</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.08082371323724984</v>
+        <v>-0.004962587064615553</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>74.22165379974524</v>
+        <v>73.70531803902978</v>
       </c>
       <c r="B30" t="n">
-        <v>151.0911540873778</v>
+        <v>89.65846750499982</v>
       </c>
       <c r="C30" t="n">
-        <v>49.77208604662018</v>
+        <v>45.43265838982907</v>
       </c>
       <c r="D30" t="n">
-        <v>9.599834595979273</v>
+        <v>10.03199203641903</v>
       </c>
       <c r="E30" t="n">
-        <v>4.040346888563563</v>
+        <v>4.178482228167361</v>
       </c>
       <c r="F30" t="n">
-        <v>10.16953378369731</v>
+        <v>10.14119141566841</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0974606212129014</v>
+        <v>0.09802793902746053</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6720896281722751</v>
+        <v>-0.6178044042725409</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.8208491379668404</v>
+        <v>-0.797730230777379</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.804588804963407</v>
+        <v>-0.7608919836615797</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.1052489158547692</v>
+        <v>-0.02637266126936704</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.4294409293555899</v>
+        <v>-0.4001503910280871</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.09636578568536432</v>
+        <v>-0.003489103235434915</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>51.5458385319972</v>
+        <v>81.20992533576073</v>
       </c>
       <c r="B31" t="n">
-        <v>140.0270369637499</v>
+        <v>109.8551863092569</v>
       </c>
       <c r="C31" t="n">
-        <v>49.04775725989096</v>
+        <v>45.46831025472342</v>
       </c>
       <c r="D31" t="n">
-        <v>11.23252613983096</v>
+        <v>9.964975888710221</v>
       </c>
       <c r="E31" t="n">
-        <v>3.850171869394191</v>
+        <v>4.027473071814707</v>
       </c>
       <c r="F31" t="n">
-        <v>6.557019337351027</v>
+        <v>11.77022439594422</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3752615931178852</v>
+        <v>0.06983846655997707</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.04712010603655467</v>
+        <v>-0.7109932696667031</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5915759006939829</v>
+        <v>-0.8378507872308315</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.194649609010324</v>
+        <v>-0.8348643025829873</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.01015691101867058</v>
+        <v>-0.1548190820376894</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.2600510081222658</v>
+        <v>-0.4536207180172952</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.09318585311967623</v>
+        <v>-0.01126769193965552</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>78.70053105867412</v>
+        <v>60.99023262955456</v>
       </c>
       <c r="B32" t="n">
-        <v>172.2938807116515</v>
+        <v>112.9488317880823</v>
       </c>
       <c r="C32" t="n">
-        <v>49.96153173621003</v>
+        <v>45.91212294470558</v>
       </c>
       <c r="D32" t="n">
-        <v>9.067957243911346</v>
+        <v>11.35555605110292</v>
       </c>
       <c r="E32" t="n">
-        <v>3.339954144500713</v>
+        <v>3.841413075659375</v>
       </c>
       <c r="F32" t="n">
-        <v>10.99772451069471</v>
+        <v>8.074086843554241</v>
       </c>
       <c r="G32" t="n">
-        <v>0.07909583183088191</v>
+        <v>0.196233116897967</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7231279617639605</v>
+        <v>-0.3347070591070645</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8434656251575608</v>
+        <v>-0.6888714557912099</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8438312806474143</v>
+        <v>-0.5008995804780434</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.09806755083365945</v>
+        <v>-0.06524316074011248</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.4628984547916328</v>
+        <v>-0.3095554074855762</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.08745498058502173</v>
+        <v>-0.1080995515721274</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>89.17424109652173</v>
+        <v>76.48325514917499</v>
       </c>
       <c r="B33" t="n">
-        <v>141.6826914708712</v>
+        <v>86.48091237764112</v>
       </c>
       <c r="C33" t="n">
-        <v>49.74965880488828</v>
+        <v>45.41920281169065</v>
       </c>
       <c r="D33" t="n">
-        <v>7.669874597189818</v>
+        <v>9.788363077445689</v>
       </c>
       <c r="E33" t="n">
-        <v>4.975685698416492</v>
+        <v>4.282945139479365</v>
       </c>
       <c r="F33" t="n">
-        <v>13.10700472183374</v>
+        <v>10.67053212899917</v>
       </c>
       <c r="G33" t="n">
-        <v>0.05120428514361882</v>
+        <v>0.08593147342493605</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8063518944697196</v>
+        <v>-0.6566868620138973</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8828473303607117</v>
+        <v>-0.8141515427020066</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.9027021310912247</v>
+        <v>-0.792592647070793</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.05217939437028515</v>
+        <v>-0.03119412935908664</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.5411377991055307</v>
+        <v>-0.4199431929378719</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.0975813090882858</v>
+        <v>-0.0005533407325040984</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>93.82650795069891</v>
+        <v>60.51365333041471</v>
       </c>
       <c r="B34" t="n">
-        <v>148.8165931895767</v>
+        <v>103.7947100819603</v>
       </c>
       <c r="C34" t="n">
-        <v>49.91219951525036</v>
+        <v>45.43556457099841</v>
       </c>
       <c r="D34" t="n">
-        <v>6.969839550475269</v>
+        <v>10.94436486384879</v>
       </c>
       <c r="E34" t="n">
-        <v>3.883223334266139</v>
+        <v>4.489462080379048</v>
       </c>
       <c r="F34" t="n">
-        <v>14.12469612742828</v>
+        <v>7.862114668933168</v>
       </c>
       <c r="G34" t="n">
-        <v>0.04309741648915581</v>
+        <v>0.2010987119516803</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8323208775754125</v>
+        <v>-0.3282804756237267</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8959452372153173</v>
+        <v>-0.6884242682137187</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9195652026448417</v>
+        <v>-0.4961621065379737</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.02632163208910234</v>
+        <v>-0.02569582283523204</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.5758905569085244</v>
+        <v>-0.3288523999781103</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.09009146877067201</v>
+        <v>-0.004123179126925142</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>55.44659084531989</v>
+        <v>80.63904842948422</v>
       </c>
       <c r="B35" t="n">
-        <v>154.2251628596252</v>
+        <v>114.2043134333062</v>
       </c>
       <c r="C35" t="n">
-        <v>49.0365745932382</v>
+        <v>43.35450408851293</v>
       </c>
       <c r="D35" t="n">
-        <v>10.91133018878947</v>
+        <v>9.920647295423716</v>
       </c>
       <c r="E35" t="n">
-        <v>3.904264864678813</v>
+        <v>4.948595619958433</v>
       </c>
       <c r="F35" t="n">
-        <v>7.061201153245497</v>
+        <v>11.70902628017412</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2844917876508187</v>
+        <v>0.07167742618217124</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2317158488652286</v>
+        <v>-0.7049478101476042</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6530773422476526</v>
+        <v>-0.8351166262665568</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.3951324106472737</v>
+        <v>-0.8302593236289892</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.0104966137981466</v>
+        <v>-0.09445037650134447</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.2891898999020125</v>
+        <v>-0.449553220060075</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.09241429478970344</v>
+        <v>-0.3934758858444697</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>71.24495911802653</v>
+        <v>73.1805609808212</v>
       </c>
       <c r="B36" t="n">
-        <v>149.6148008909069</v>
+        <v>86.48091237764112</v>
       </c>
       <c r="C36" t="n">
-        <v>48.78533217750075</v>
+        <v>45.41920281169065</v>
       </c>
       <c r="D36" t="n">
-        <v>9.542480169855875</v>
+        <v>9.788363077445689</v>
       </c>
       <c r="E36" t="n">
-        <v>2.859484443460446</v>
+        <v>4.282945139479365</v>
       </c>
       <c r="F36" t="n">
-        <v>9.520298283228025</v>
+        <v>9.971740714122037</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1125565571335915</v>
+        <v>0.1003712533794091</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6310952519142705</v>
+        <v>-0.6141146773876363</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8034311751614467</v>
+        <v>-0.7972728732649909</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.7716055574936136</v>
+        <v>-0.7584640092825197</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.0168030901351577</v>
+        <v>-0.004393149387572899</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.4072048125184085</v>
+        <v>-0.410132852172255</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.07713198235607906</v>
+        <v>-0.0005533407325040984</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>81.3149122844728</v>
+        <v>78.73469576315473</v>
       </c>
       <c r="B37" t="n">
-        <v>152.8762906677482</v>
+        <v>115.6370144867573</v>
       </c>
       <c r="C37" t="n">
-        <v>48.80260767211551</v>
+        <v>45.42830131665562</v>
       </c>
       <c r="D37" t="n">
-        <v>9.175402343998195</v>
+        <v>10.06826099553797</v>
       </c>
       <c r="E37" t="n">
-        <v>4.604370522366101</v>
+        <v>4.683835277746614</v>
       </c>
       <c r="F37" t="n">
-        <v>11.58481467104899</v>
+        <v>11.23371868868527</v>
       </c>
       <c r="G37" t="n">
-        <v>0.07062615378685749</v>
+        <v>0.07778976261998283</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7478329511906968</v>
+        <v>-0.6840629811209824</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8547576561105897</v>
+        <v>-0.8259367848604633</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.8619973008334159</v>
+        <v>-0.8141860344731537</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.1547398540744607</v>
+        <v>-0.1257885563314853</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.4824280648489958</v>
+        <v>-0.4359847073124775</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.07831177089190208</v>
+        <v>-0.00253846908849914</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>52.09521977057393</v>
+        <v>67.91161734780292</v>
       </c>
       <c r="B38" t="n">
-        <v>176.7759717569227</v>
+        <v>100.4540457725244</v>
       </c>
       <c r="C38" t="n">
-        <v>48.7928302055212</v>
+        <v>45.42950429928512</v>
       </c>
       <c r="D38" t="n">
-        <v>11.2020658443409</v>
+        <v>10.50899601953465</v>
       </c>
       <c r="E38" t="n">
-        <v>3.370596568269477</v>
+        <v>4.388237003413707</v>
       </c>
       <c r="F38" t="n">
-        <v>6.62303419028551</v>
+        <v>9.098103895821499</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3603540844201486</v>
+        <v>0.1317031622040402</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.07654191148398783</v>
+        <v>-0.5148928278156413</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6011378170448379</v>
+        <v>-0.7562620454135619</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.2275534816572848</v>
+        <v>-0.6719368001215417</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.007632148937171136</v>
+        <v>-0.01459891407909443</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.2641549242827549</v>
+        <v>-0.3588702736030958</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.07764404222452727</v>
+        <v>-0.002800938025845495</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>90.70781442165696</v>
+        <v>90.68628123261105</v>
       </c>
       <c r="B39" t="n">
-        <v>148.0188812178639</v>
+        <v>108.0480655488848</v>
       </c>
       <c r="C39" t="n">
-        <v>48.78947033922839</v>
+        <v>45.43686473130203</v>
       </c>
       <c r="D39" t="n">
-        <v>7.663191296008617</v>
+        <v>8.22967661280064</v>
       </c>
       <c r="E39" t="n">
-        <v>4.593198973655319</v>
+        <v>4.122114015496829</v>
       </c>
       <c r="F39" t="n">
-        <v>13.47179102879497</v>
+        <v>13.64563415613044</v>
       </c>
       <c r="G39" t="n">
-        <v>0.04834507284743964</v>
+        <v>0.04759427696081772</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8154659422400384</v>
+        <v>-0.7895819037400231</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8873812444556431</v>
+        <v>-0.874559613896833</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.9087069778408938</v>
+        <v>-0.8915279602218517</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.0793996297579245</v>
+        <v>-0.02136938989493574</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.5525936987802673</v>
+        <v>-0.5211397537823538</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.07741458820178893</v>
+        <v>-0.004406850465898116</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>85.19289587770623</v>
+        <v>55.78201147597592</v>
       </c>
       <c r="B40" t="n">
-        <v>151.1211534540476</v>
+        <v>114.342435612665</v>
       </c>
       <c r="C40" t="n">
-        <v>48.78558277747646</v>
+        <v>45.42089036899194</v>
       </c>
       <c r="D40" t="n">
-        <v>8.049980676896613</v>
+        <v>11.48608747660235</v>
       </c>
       <c r="E40" t="n">
-        <v>3.505652785333848</v>
+        <v>4.196773818937647</v>
       </c>
       <c r="F40" t="n">
-        <v>12.20745161264776</v>
+        <v>7.216192169638799</v>
       </c>
       <c r="G40" t="n">
-        <v>0.05982996971985347</v>
+        <v>0.2731627086933254</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.7795294905983544</v>
+        <v>-0.1353227566460266</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.8697889015966868</v>
+        <v>-0.620235992670309</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.8844989296261332</v>
+        <v>-0.2930473814803115</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.01087788668322473</v>
+        <v>-0.002741415094127609</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.5113968727020144</v>
+        <v>-0.2724468317663284</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.07714909648131954</v>
+        <v>-0.0009215350527877475</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>55.56987355514711</v>
+        <v>87.48266244295034</v>
       </c>
       <c r="B41" t="n">
-        <v>146.3739227000343</v>
+        <v>131.1488900549178</v>
       </c>
       <c r="C41" t="n">
-        <v>49.44034648676463</v>
+        <v>45.45310175202545</v>
       </c>
       <c r="D41" t="n">
-        <v>11.21172963612882</v>
+        <v>8.65880128378709</v>
       </c>
       <c r="E41" t="n">
-        <v>4.735723522404118</v>
+        <v>4.99321442358135</v>
       </c>
       <c r="F41" t="n">
-        <v>7.171125793548581</v>
+        <v>12.94475417468382</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2830672736309084</v>
+        <v>0.05380441798847824</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.2361147109689327</v>
+        <v>-0.7668144635184294</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6544785823461768</v>
+        <v>-0.8636340571481507</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.3996157850525958</v>
+        <v>-0.875734426691349</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.07199321609245217</v>
+        <v>-0.03660850087327773</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.2901108303409178</v>
+        <v>-0.4983139699060211</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.1071366306573498</v>
+        <v>-0.007949473169189675</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>50.93202429563714</v>
+        <v>55.02912977787617</v>
       </c>
       <c r="B42" t="n">
-        <v>137.4978542953568</v>
+        <v>110.3045336664186</v>
       </c>
       <c r="C42" t="n">
-        <v>49.44818687547517</v>
+        <v>45.4321840631832</v>
       </c>
       <c r="D42" t="n">
-        <v>11.22932468793069</v>
+        <v>11.29528553061932</v>
       </c>
       <c r="E42" t="n">
-        <v>4.062508935532795</v>
+        <v>4.028057619124123</v>
       </c>
       <c r="F42" t="n">
-        <v>6.482863252263424</v>
+        <v>7.05213939003646</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3928219103539272</v>
+        <v>0.2868927738150112</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.01275627283188216</v>
+        <v>-0.1119036839321498</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.5805162588210958</v>
+        <v>-0.6147295983834661</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.1558010369638849</v>
+        <v>-0.2699433448702982</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.008750214892102563</v>
+        <v>-0.0005201496742767832</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.255465772975426</v>
+        <v>-0.2877184733340713</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.1071074875055505</v>
+        <v>-0.003385613785426428</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>51.32056851303667</v>
+        <v>90.04055919515598</v>
       </c>
       <c r="B43" t="n">
-        <v>139.9179962186716</v>
+        <v>131.1488900549178</v>
       </c>
       <c r="C43" t="n">
-        <v>48.76420163530666</v>
+        <v>45.45310175202545</v>
       </c>
       <c r="D43" t="n">
-        <v>11.23260885644989</v>
+        <v>8.65880128378709</v>
       </c>
       <c r="E43" t="n">
-        <v>3.850171869394191</v>
+        <v>4.974585153006991</v>
       </c>
       <c r="F43" t="n">
-        <v>6.525154153420973</v>
+        <v>13.58670323533333</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3815324728590944</v>
+        <v>0.04884120106666918</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.0347327035134403</v>
+        <v>-0.7851470060085908</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5875825784695745</v>
+        <v>-0.8723751734758138</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.1807028386642601</v>
+        <v>-0.8884821187705542</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.0011951440107171</v>
+        <v>-0.1000897008017469</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.2583682253725656</v>
+        <v>-0.5165389842654864</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.07596120239372231</v>
+        <v>-0.007949473169189675</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>60.15282660749823</v>
+        <v>56.32748701259196</v>
       </c>
       <c r="B44" t="n">
-        <v>173.9379610593086</v>
+        <v>113.9817946461167</v>
       </c>
       <c r="C44" t="n">
-        <v>48.78662734019051</v>
+        <v>45.42076009108757</v>
       </c>
       <c r="D44" t="n">
-        <v>10.58238475057583</v>
+        <v>11.48637533537224</v>
       </c>
       <c r="E44" t="n">
-        <v>4.532764603881065</v>
+        <v>4.105625637059457</v>
       </c>
       <c r="F44" t="n">
-        <v>7.736256601329493</v>
+        <v>7.302707694123892</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2096145888589234</v>
+        <v>0.263433091081112</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.3953476980388018</v>
+        <v>-0.1597250206694851</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.7111724175640306</v>
+        <v>-0.6283742971650931</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.5599821724185141</v>
+        <v>-0.3194301231044868</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.01955584046399796</v>
+        <v>-0.01051968300200724</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.3243458092110236</v>
+        <v>-0.2763333449647176</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.07722043239050574</v>
+        <v>-0.0008931107827421514</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>92.96144142211412</v>
+        <v>55.02912977787617</v>
       </c>
       <c r="B45" t="n">
-        <v>153.1850499760033</v>
+        <v>110.6730390535578</v>
       </c>
       <c r="C45" t="n">
-        <v>49.82979408129959</v>
+        <v>45.4321840631832</v>
       </c>
       <c r="D45" t="n">
-        <v>7.634697036388579</v>
+        <v>11.29528553061932</v>
       </c>
       <c r="E45" t="n">
-        <v>3.924849202545774</v>
+        <v>4.480246616931666</v>
       </c>
       <c r="F45" t="n">
-        <v>14.06362533270335</v>
+        <v>7.05213939003646</v>
       </c>
       <c r="G45" t="n">
-        <v>0.04456849022103664</v>
+        <v>0.2868927738150112</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.8277639267438383</v>
+        <v>-0.1119036839321498</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.8935716365551831</v>
+        <v>-0.6147295983834661</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.9166526953018423</v>
+        <v>-0.2699433448702982</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.1605313093257515</v>
+        <v>-0.0005201496742767832</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.5694284496189587</v>
+        <v>-0.2877184733340713</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.09430944458442271</v>
+        <v>-0.003385613785426428</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>54.69354709360198</v>
+        <v>92.75907824694843</v>
       </c>
       <c r="B46" t="n">
-        <v>151.0235471717868</v>
+        <v>89.54243697398945</v>
       </c>
       <c r="C46" t="n">
-        <v>48.82919888782472</v>
+        <v>45.4199322663697</v>
       </c>
       <c r="D46" t="n">
-        <v>11.07879862590434</v>
+        <v>8.96354473586036</v>
       </c>
       <c r="E46" t="n">
-        <v>3.881493983628592</v>
+        <v>4.140021378952543</v>
       </c>
       <c r="F46" t="n">
-        <v>6.983526747011805</v>
+        <v>14.36243446653505</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2998327322746635</v>
+        <v>0.04429246861206414</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.1999558537109258</v>
+        <v>-0.8024250328071235</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6421923917705263</v>
+        <v>-0.8807587761004108</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.3616445576983952</v>
+        <v>-0.9001681170844932</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.02486497194679928</v>
+        <v>-0.2225201196788639</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.2835646105669837</v>
+        <v>-0.5359084325095076</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.08012775429190927</v>
+        <v>-0.0007124944806610745</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>89.88414662824285</v>
+        <v>55.78201147597592</v>
       </c>
       <c r="B47" t="n">
-        <v>158.4925915176813</v>
+        <v>114.342435612665</v>
       </c>
       <c r="C47" t="n">
-        <v>49.38298844461331</v>
+        <v>45.42089036899194</v>
       </c>
       <c r="D47" t="n">
-        <v>7.706432492726041</v>
+        <v>11.48608747660235</v>
       </c>
       <c r="E47" t="n">
-        <v>2.969780623242905</v>
+        <v>4.207513036982167</v>
       </c>
       <c r="F47" t="n">
-        <v>13.28599200751581</v>
+        <v>7.216192169638799</v>
       </c>
       <c r="G47" t="n">
-        <v>0.04986224552871126</v>
+        <v>0.2731627086933254</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.8106369617818849</v>
+        <v>-0.1353227566460266</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.8849686094382569</v>
+        <v>-0.620235992670309</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.9055361370940793</v>
+        <v>-0.2930473814803115</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.0756648373580576</v>
+        <v>-0.002741415094127609</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.5464408429291578</v>
+        <v>-0.2724468317663284</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.1073498336235586</v>
+        <v>-0.0009215350527877475</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>52.58966303824361</v>
+        <v>61.66734389898767</v>
       </c>
       <c r="B48" t="n">
-        <v>167.1876205418745</v>
+        <v>113.9817946461167</v>
       </c>
       <c r="C48" t="n">
-        <v>49.30554835286635</v>
+        <v>45.42076009108757</v>
       </c>
       <c r="D48" t="n">
-        <v>11.27528402039733</v>
+        <v>11.02884187301754</v>
       </c>
       <c r="E48" t="n">
-        <v>4.555884403282354</v>
+        <v>4.169842357223974</v>
       </c>
       <c r="F48" t="n">
-        <v>6.727079642687746</v>
+        <v>8.081235766545712</v>
       </c>
       <c r="G48" t="n">
-        <v>0.3481732641707295</v>
+        <v>0.1877446299301792</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.1016249009667654</v>
+        <v>-0.3564723068681232</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.6092984721007819</v>
+        <v>-0.6968085048883504</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.2552586925679303</v>
+        <v>-0.5225667203467657</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.03755297105142948</v>
+        <v>-0.009015539714348226</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.267848449969747</v>
+        <v>-0.3143798252802871</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.1071685304455079</v>
+        <v>-0.0008931107827421514</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>53.09856928179287</v>
+        <v>58.66700371091607</v>
       </c>
       <c r="B49" t="n">
-        <v>130.0000936962097</v>
+        <v>113.6100214422858</v>
       </c>
       <c r="C49" t="n">
-        <v>48.82757231249705</v>
+        <v>45.46815231884445</v>
       </c>
       <c r="D49" t="n">
-        <v>11.0792315392492</v>
+        <v>11.35602713324175</v>
       </c>
       <c r="E49" t="n">
-        <v>3.907695506340735</v>
+        <v>3.838635672019076</v>
       </c>
       <c r="F49" t="n">
-        <v>6.742271776146761</v>
+        <v>7.653977495351725</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3350259994312426</v>
+        <v>0.2262588808295556</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1272027431121982</v>
+        <v>-0.2546186367169823</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.6178130362536864</v>
+        <v>-0.6607207131608559</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.2833939445687242</v>
+        <v>-0.4196148978900506</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.001202503289486382</v>
+        <v>-0.02266569425560255</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.271650015095062</v>
+        <v>-0.293002401440277</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.08001667122499632</v>
+        <v>-0.01123323320242467</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>71.9572976380245</v>
+        <v>87.48266244295034</v>
       </c>
       <c r="B50" t="n">
-        <v>141.8917601308196</v>
+        <v>134.2417554256178</v>
       </c>
       <c r="C50" t="n">
-        <v>49.9189452151966</v>
+        <v>45.45310175202545</v>
       </c>
       <c r="D50" t="n">
-        <v>9.955273997501024</v>
+        <v>8.65880128378709</v>
       </c>
       <c r="E50" t="n">
-        <v>2.356421066791512</v>
+        <v>4.912556624960994</v>
       </c>
       <c r="F50" t="n">
-        <v>9.795503538454486</v>
+        <v>12.94475417468382</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1090494558379477</v>
+        <v>0.05380441798847824</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.6412080221674136</v>
+        <v>-0.7668144635184294</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.8075976608663026</v>
+        <v>-0.8636340571481507</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.7798143692963012</v>
+        <v>-0.875734426691349</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.1296045915770198</v>
+        <v>-0.03660850087327773</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.4125260309341158</v>
+        <v>-0.4983139699060211</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.08973095473205253</v>
+        <v>-0.007949473169189675</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>74.85190386602409</v>
+        <v>93.13164304496333</v>
       </c>
       <c r="B51" t="n">
-        <v>145.1729027613802</v>
+        <v>114.0208132078782</v>
       </c>
       <c r="C51" t="n">
-        <v>49.34840387671773</v>
+        <v>45.42165501431086</v>
       </c>
       <c r="D51" t="n">
-        <v>9.8067968519007</v>
+        <v>8.726489766912351</v>
       </c>
       <c r="E51" t="n">
-        <v>3.387986209325125</v>
+        <v>4.614861175343319</v>
       </c>
       <c r="F51" t="n">
-        <v>10.34005368323444</v>
+        <v>14.40228257890642</v>
       </c>
       <c r="G51" t="n">
-        <v>0.09469006179736451</v>
+        <v>0.04366280012139699</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.6798949168875896</v>
+        <v>-0.8047122324777874</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8242116034855271</v>
+        <v>-0.8819072089211357</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.8107140150855158</v>
+        <v>-0.9016986197773502</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.1470287898587036</v>
+        <v>-0.1889289136263391</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.4341489412979925</v>
+        <v>-0.5385629566953636</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1074783863457893</v>
+        <v>-0.001088366758734277</v>
       </c>
     </row>
   </sheetData>
